--- a/july 2026/Price List.xlsx
+++ b/july 2026/Price List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF9C6F9-0536-44A1-8F1D-2AFB9F9FB83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31A728E-6E8A-4F91-81C6-46934BB3CEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{436D651F-ACC5-44DC-A5CE-EF0963C481FB}"/>
   </bookViews>
